--- a/app/static/library/ambiente/allegati/ALLEGATO 3 - ORGANIGRAMMA AZIENDALE.xlsx
+++ b/app/static/library/ambiente/allegati/ALLEGATO 3 - ORGANIGRAMMA AZIENDALE.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
